--- a/J30/Australia_Impact/Input_files/Inbound_worksheet.xlsx
+++ b/J30/Australia_Impact/Input_files/Inbound_worksheet.xlsx
@@ -129,10 +129,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -759,12 +759,17 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>vgana3</t>
         </is>
       </c>
-      <c r="J2" s="9" t="inlineStr">
+      <c r="J2" s="8" t="inlineStr">
         <is>
           <t>*************</t>
         </is>
@@ -854,12 +859,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0508314880</t>
+          <t>0508312890</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00081083120260000001;00081083120260000002</t>
+          <t>00081083120260000007;00081083120260000008</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -874,7 +879,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>93002349</t>
+          <t>93002353</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -889,12 +894,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Apt-00000000000011332</t>
+          <t>Apt-00000000000011335</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>T08312601</t>
+          <t>T08312603</t>
         </is>
       </c>
     </row>

--- a/J30/Australia_Impact/Input_files/Inbound_worksheet.xlsx
+++ b/J30/Australia_Impact/Input_files/Inbound_worksheet.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="34140" windowHeight="28200" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CreateASN" sheetId="1" state="visible" r:id="rId1"/>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>180</v>
       </c>
       <c r="G2" t="n">
         <v>6</v>
@@ -859,12 +859,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0508312890</t>
+          <t>0509014110</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00081083120260000007;00081083120260000008</t>
+          <t>00081090120260000091;00081090120260000092;00081090120260000093;00081090120260000094;00081090120260000095;00081090120260000096;00081090120260000097;00081090120260000098;00081090120260000099;00081090120260000100;00081090120260000101;00081090120260000102;00081090120260000103;00081090120260000104;00081090120260000105;00081090120260000106;00081090120260000107;00081090120260000108;00081090120260000109;00081090120260000110;00081090120260000111;00081090120260000112;00081090120260000113;00081090120260000114;00081090120260000115;00081090120260000116;00081090120260000117;00081090120260000118;00081090120260000119;00081090120260000120</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>93002353</t>
+          <t>93002356</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Apt-00000000000011335</t>
+          <t>Apt-00000000000011338</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>T08312603</t>
+          <t>T09012603</t>
         </is>
       </c>
     </row>

--- a/J30/Australia_Impact/Input_files/Inbound_worksheet.xlsx
+++ b/J30/Australia_Impact/Input_files/Inbound_worksheet.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="34140" windowHeight="28200" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="34140" windowHeight="28200" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CreateASN" sheetId="1" state="visible" r:id="rId1"/>
@@ -118,7 +118,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -132,6 +132,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -764,6 +767,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>vgana3</t>
@@ -786,63 +794,73 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Plant</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>ASNID</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>LPNID</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>Pre_Allocate</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>InboundDelivery</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>IB_Delivery_QTY</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>LocationId</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="J1" s="11" t="inlineStr">
         <is>
           <t>Appt_id</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="K1" s="11" t="inlineStr">
         <is>
           <t>TrailerId</t>
+        </is>
+      </c>
+      <c r="L1" s="11" t="inlineStr">
+        <is>
+          <t>PalletId</t>
+        </is>
+      </c>
+      <c r="M1" s="11" t="inlineStr">
+        <is>
+          <t>DropLocation</t>
         </is>
       </c>
     </row>
@@ -859,12 +877,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0509014110</t>
+          <t>0509026600</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00081090120260000091;00081090120260000092;00081090120260000093;00081090120260000094;00081090120260000095;00081090120260000096;00081090120260000097;00081090120260000098;00081090120260000099;00081090120260000100;00081090120260000101;00081090120260000102;00081090120260000103;00081090120260000104;00081090120260000105;00081090120260000106;00081090120260000107;00081090120260000108;00081090120260000109;00081090120260000110;00081090120260000111;00081090120260000112;00081090120260000113;00081090120260000114;00081090120260000115;00081090120260000116;00081090120260000117;00081090120260000118;00081090120260000119;00081090120260000120</t>
+          <t>00081090220260000091;00081090220260000092;00081090220260000093;00081090220260000094;00081090220260000095;00081090220260000096;00081090220260000097;00081090220260000098;00081090220260000099;00081090220260000100;00081090220260000101;00081090220260000102;00081090220260000103;00081090220260000104;00081090220260000105;00081090220260000106;00081090220260000107;00081090220260000108;00081090220260000109;00081090220260000110;00081090220260000111;00081090220260000112;00081090220260000113;00081090220260000114;00081090220260000115;00081090220260000116;00081090220260000117;00081090220260000118;00081090220260000119;00081090220260000120</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -879,7 +897,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>93002356</t>
+          <t>93002360</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -894,12 +912,22 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Apt-00000000000011338</t>
+          <t>Apt-00000000000011341</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>T09012603</t>
+          <t>T09022602</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>PAL09022603;PAL09022602</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1034VNA011</t>
         </is>
       </c>
     </row>

--- a/J30/Australia_Impact/Input_files/Inbound_worksheet.xlsx
+++ b/J30/Australia_Impact/Input_files/Inbound_worksheet.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="34140" windowHeight="28200" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="780" windowWidth="34140" windowHeight="22600" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CreateASN" sheetId="1" state="visible" r:id="rId1"/>
@@ -118,7 +118,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -132,9 +132,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -635,7 +632,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>180</v>
+        <v>12</v>
       </c>
       <c r="G2" t="n">
         <v>6</v>
@@ -772,6 +769,16 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>vgana3</t>
@@ -798,67 +805,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Plant</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>ASNID</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>LPNID</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>Pre_Allocate</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>InboundDelivery</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>IB_Delivery_QTY</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>LocationId</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>Appt_id</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>TrailerId</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>PalletId</t>
         </is>
       </c>
-      <c r="M1" s="11" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>DropLocation</t>
         </is>
@@ -877,12 +884,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0509026600</t>
+          <t>0509038070</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00081090220260000091;00081090220260000092;00081090220260000093;00081090220260000094;00081090220260000095;00081090220260000096;00081090220260000097;00081090220260000098;00081090220260000099;00081090220260000100;00081090220260000101;00081090220260000102;00081090220260000103;00081090220260000104;00081090220260000105;00081090220260000106;00081090220260000107;00081090220260000108;00081090220260000109;00081090220260000110;00081090220260000111;00081090220260000112;00081090220260000113;00081090220260000114;00081090220260000115;00081090220260000116;00081090220260000117;00081090220260000118;00081090220260000119;00081090220260000120</t>
+          <t>00081090320260000007;00081090320260000008</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -897,7 +904,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>93002360</t>
+          <t>93002365</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -912,22 +919,22 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Apt-00000000000011341</t>
+          <t>Apt-00000000000011346</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>T09022602</t>
+          <t>T09032603</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>PAL09022603;PAL09022602</t>
+          <t>PAL09032602</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>1034VNA011</t>
+          <t>1031VNA011</t>
         </is>
       </c>
     </row>

--- a/J30/Australia_Impact/Input_files/Inbound_worksheet.xlsx
+++ b/J30/Australia_Impact/Input_files/Inbound_worksheet.xlsx
@@ -24,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode=";;;"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -52,14 +52,6 @@
       <b val="1"/>
       <sz val="12"/>
     </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <b val="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -69,7 +61,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -92,33 +84,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -130,12 +101,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -632,7 +597,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>240</v>
       </c>
       <c r="G2" t="n">
         <v>6</v>
@@ -749,32 +714,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -801,73 +741,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Plant</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>ASNID</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>LPNID</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Pre_Allocate</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>InboundDelivery</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>IB_Delivery_QTY</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>LocationId</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Appt_id</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>TrailerId</t>
         </is>
       </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>PalletId</t>
-        </is>
-      </c>
-      <c r="M1" s="10" t="inlineStr">
-        <is>
-          <t>DropLocation</t>
         </is>
       </c>
     </row>
@@ -884,12 +819,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0509038070</t>
+          <t>0509042602</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00081090320260000007;00081090320260000008</t>
+          <t>00081090420260000105;00081090420260000106;00081090420260000107;00081090420260000108;00081090420260000109;00081090420260000110;00081090420260000111;00081090420260000112;00081090420260000113;00081090420260000114;00081090420260000115;00081090420260000116;00081090420260000117;00081090420260000118;00081090420260000119;00081090420260000120;00081090420260000121;00081090420260000122;00081090420260000123;00081090420260000124;00081090420260000125;00081090420260000126;00081090420260000127;00081090420260000128;00081090420260000129;00081090420260000130;00081090420260000131;00081090420260000132;00081090420260000133;00081090420260000134;00081090420260000135;00081090420260000136;00081090420260000137;00081090420260000138;00081090420260000139;00081090420260000140;00081090420260000141;00081090420260000142;00081090420260000143;00081090420260000144</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -904,7 +839,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>93002365</t>
+          <t>93002375</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -919,22 +854,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Apt-00000000000011346</t>
+          <t>Apt-00000000000011356</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>T09032603</t>
+          <t>T09042610</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>PAL09032602</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>1031VNA011</t>
+          <t>PAL09042614;PAL09042613</t>
         </is>
       </c>
     </row>
